--- a/tools/_out/brennancad_20261021/regen/stage/tee/DesignTable_6503_SW2.xlsx
+++ b/tools/_out/brennancad_20261021/regen/stage/tee/DesignTable_6503_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG2"/>
+  <dimension ref="A1:BG5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -904,6 +904,603 @@
       <c r="BG2" t="inlineStr">
         <is>
           <t>6503-08-08-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>6503-04-04-FG</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.1465</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.649</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.2574</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.2796</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.3268</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.32505</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.21875</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.19169</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.5243</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.1845</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.3268</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.25944</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.38338</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.2867</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0.19169</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0.21875</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0.21601</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0.21601</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0.43251</v>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>6503-04-04-FG</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>90 deg Female Pipe x Female Swivel Elbow, 1/4-18 NPTF (female) x 7/16-20 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>6503</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>1/4-18 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>7/16-20 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] [BRENNAN-CAD 2026-10-21: M5@DRIVE, N1@DRIVE, M10@DRIVE, C3HEX@HEX, Y1@HEX, D@BORE, THDMAJ_A@DRIVE, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6503-04-04 (differs by -FG suffix) -&gt; dims NOT copied | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the part's own D column (ASSUMPTION; capped at the tap drill where larger); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6503-04-04 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6503-04-04-FG (PARTcommunity / CADENAS, M5@DRIVE=M6, N1@DRIVE=M2, M10@DRIVE=M4, C3HEX@HEX=C, Y1@HEX=Y, D@BORE=BD, THDMAJ_A@DRIVE=ATHD, THDMAJ_B@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL@BORE = Air-Way per-size tap drill -04 0.43 (A1)</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>6503-04-04-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>6503-06-06-FG</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.3428</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.3876</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.39722</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.25118</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.2945</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.2925</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.5953000000000001</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.246</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.3876</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.32944</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.50236</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.3197</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.25118</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.25209</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0.25209</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0.50468</v>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>6503-06-06-FG</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>90 deg Female Pipe x Female Swivel Elbow, 3/8-18 NPTF (female) x 9/16-18 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>6503</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>3/8-18 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>9/16-18 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] [BRENNAN-CAD 2026-10-21: M5@DRIVE, N1@DRIVE, M10@DRIVE, C3HEX@HEX, Y1@HEX, D@BORE, THDMAJ_A@DRIVE, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6503-06-06 (differs by -FG suffix) -&gt; dims NOT copied | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the part's own D column (ASSUMPTION; capped at the tap drill where larger); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6503-06-06 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6503-06-06-FG (PARTcommunity / CADENAS, M5@DRIVE=M6, N1@DRIVE=M2, M10@DRIVE=M4, C3HEX@HEX=C, Y1@HEX=Y, D@BORE=BD, THDMAJ_A@DRIVE=ATHD, THDMAJ_B@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL@BORE = Air-Way per-size tap drill -06 0.57 (A1)</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>6503-06-06-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>6503-12-12-FG</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.089</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.047</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.5928</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.6237</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.5998</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.7216900000000001</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.48614</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.4472</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.549</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.8623</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.481</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.4225</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.5998</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.51214</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.97228</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.4851</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.48614</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0.37824</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0.37824</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0.75698</v>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>6503-12-12-FG</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>90 deg Female Pipe x Female Swivel Elbow, 3/4-14 NPTF (female) x 1 1/16-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>6503</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>3/4-14 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>1 1/16-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] [BRENNAN-CAD 2026-10-21: M5@DRIVE, N1@DRIVE, M10@DRIVE, C3HEX@HEX, Y1@HEX, D@BORE, THDMAJ_A@DRIVE, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6503-12-12 (differs by -FG suffix) -&gt; dims NOT copied | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the part's own D column (ASSUMPTION; capped at the tap drill where larger); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6503-12-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6503-12-12-FG (PARTcommunity / CADENAS, M5@DRIVE=M6, N1@DRIVE=M2, M10@DRIVE=M4, C3HEX@HEX=C, Y1@HEX=Y, D@BORE=BD, THDMAJ_A@DRIVE=ATHD, THDMAJ_B@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL@BORE = Air-Way per-size tap drill -12 0.91 (A1) | leg 2 hex arm 0.771 barely clears the corner puck (radius 0.757)</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>6503-12-12-FG</t>
         </is>
       </c>
     </row>
